--- a/images/Dify.xlsx
+++ b/images/Dify.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df63a93e45125bfa/Documents/zenn-contents/public/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{CB262E1A-970A-45B4-96BC-1DA54D79264F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4349586-A582-4D62-86EC-13C6AE492EBE}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{CB262E1A-970A-45B4-96BC-1DA54D79264F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{320B4658-54B1-4EFF-A771-A4BD54F189A9}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="825" windowWidth="14910" windowHeight="13890" activeTab="3" xr2:uid="{0EAEFFA3-4267-4E0F-B55B-0059692EA24E}"/>
+    <workbookView xWindow="555" yWindow="825" windowWidth="14910" windowHeight="13890" activeTab="2" xr2:uid="{0EAEFFA3-4267-4E0F-B55B-0059692EA24E}"/>
   </bookViews>
   <sheets>
     <sheet name="0_セットアップ" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>https://cloud.dify.ai/signin</t>
   </si>
@@ -54,12 +54,74 @@
   <si>
     <t>→URL正規化＋重複排除→日付・バージョンをメタデータ化→再ランキングは新規性を加点。</t>
   </si>
+  <si>
+    <r>
+      <t>差分重視型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：「昨日と今日で何が変わったか？」を自動抽出する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>関係性マップ型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：情報源同士をノードリンクで可視化して返す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>時間軸ビュー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：断片情報を時系列で整理し「進化の流れ」を見せる</t>
+    </r>
+  </si>
+  <si>
+    <t>https://zenn.dev/robes/articles/a3e1a6e80efd99#%E5%85%B1%E8%B5%B7%E8%A1%8C%E5%88%97%E3%81%AE%E4%BD%9C%E6%88%90%E9%81%8E%E7%A8%8B</t>
+  </si>
+  <si>
+    <t>https://zenn.dev/fukurou_labo/articles/137b854648dad2</t>
+  </si>
+  <si>
+    <t>dify*graphrag</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【自然言語処理】【Python】共起ネットワークの作り方を理解する</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,6 +134,15 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -98,8 +169,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -531,7 +605,992 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26C991EE-9FDE-DFC4-103C-9079E36EC66C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="8096250"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6CFCEF0-262B-887A-6CDA-E0329BE41CC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="12144375"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F99B0530-B145-FCB2-05CF-8BFDF4832D54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="16192500"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46A87D13-1482-3829-9729-5214A09B7FBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="20240625"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47C2F88F-834B-75FC-91E5-C9EF02941489}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="24288750"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30F48608-CC08-A00C-024D-F4380EDB1DE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="28336875"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C97449DA-C6BC-DD68-DE4B-AAF8AE4ADD8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="32861250"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342000</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>60000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39FDC224-1DBA-27CB-C6E3-04A184013A4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="36909375"/>
+          <a:ext cx="7200000" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="吹き出し: 角を丸めた四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3790FEF-818C-570A-18FC-5CBC6B4663E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="904875" y="1295400"/>
+          <a:ext cx="3524250" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -55795"/>
+            <a:gd name="adj2" fmla="val 9857"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>あなたの興味のある分野を教えてください。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>例：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>python</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ライブラリ・巨大データの扱い・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>LLM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>モデル・</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>生成</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>AI</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>・自然言語処理・機械学習・画像</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="吹き出し: 角を丸めた四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4EF912-2688-4529-AA53-73B7B97AC23D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="704850" y="2295525"/>
+          <a:ext cx="3524250" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -55795"/>
+            <a:gd name="adj2" fmla="val 9857"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>python</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ライブラリ・巨大データの扱い</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="吹き出し: 角を丸めた四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90FB16B2-7F71-428A-BACC-59C190A20429}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="704850" y="2905125"/>
+          <a:ext cx="3524250" cy="409575"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -55795"/>
+            <a:gd name="adj2" fmla="val 9857"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>LLM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>モデル・生成</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>AI</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>・自然言語処理</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="吹き出し: 角を丸めた四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF747B6A-9AF0-4F7E-BF8C-52BA19F83687}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="904875" y="3562350"/>
+          <a:ext cx="3524250" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -55795"/>
+            <a:gd name="adj2" fmla="val 9857"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>（会話回数判定・入力内容確認・</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>会話内容整理・質問分類器）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="吹き出し: 角を丸めた四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31F778AF-B228-44C4-8201-3032161235E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="904875" y="4381499"/>
+          <a:ext cx="3524250" cy="666751"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -55795"/>
+            <a:gd name="adj2" fmla="val 9857"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>URLcontext(?)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>で検索・名詞を抽出・共起行列を</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>作成）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -870,31 +1929,67 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57F7640A-C5B1-4B09-B19D-37E546D1AF72}">
-  <dimension ref="B2:B5"/>
+  <dimension ref="B2:I20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I13" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I20" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>